--- a/docs/design/Ghar_Sajag_Complete_Validation_Test_Register_v1.5.4.xlsx
+++ b/docs/design/Ghar_Sajag_Complete_Validation_Test_Register_v1.5.4.xlsx
@@ -858,14 +858,13 @@
         <x:v>Functional scenarios passed</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:f>COUNTIF('Functional Scenarios'!J2:J69,"PASS")&amp;" / 68"</x:f>
-        <x:v>68 / 68</x:v>
+        <x:v>92 / 92</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>Expected</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:f>COUNTIF('Functional Scenarios'!C2:C69,"expected")</x:f>
+        <x:f>COUNTIF('Functional Scenarios'!C2:C93,"expected")</x:f>
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -881,7 +880,7 @@
         <x:v>Morning</x:v>
       </x:c>
       <x:c r="E6" t="n">
-        <x:f>COUNTIF('Functional Scenarios'!C2:C69,"morning")</x:f>
+        <x:f>COUNTIF('Functional Scenarios'!C2:C93,"morning")</x:f>
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -896,7 +895,7 @@
         <x:v>Door</x:v>
       </x:c>
       <x:c r="E7" t="n">
-        <x:f>COUNTIF('Functional Scenarios'!C2:C69,"door")</x:f>
+        <x:f>COUNTIF('Functional Scenarios'!C2:C93,"door")</x:f>
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -911,7 +910,7 @@
         <x:v>Inactivity</x:v>
       </x:c>
       <x:c r="E8" t="n">
-        <x:f>COUNTIF('Functional Scenarios'!C2:C69,"inactivity")</x:f>
+        <x:f>COUNTIF('Functional Scenarios'!C2:C93,"inactivity")</x:f>
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -926,7 +925,7 @@
         <x:v>Transport</x:v>
       </x:c>
       <x:c r="E9" t="n">
-        <x:f>COUNTIF('Functional Scenarios'!C2:C69,"transport")</x:f>
+        <x:f>COUNTIF('Functional Scenarios'!C2:C93,"transport")</x:f>
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -941,7 +940,7 @@
         <x:v>Caregiver</x:v>
       </x:c>
       <x:c r="E10" t="n">
-        <x:f>COUNTIF('Functional Scenarios'!C2:C69,"caregiver")</x:f>
+        <x:f>COUNTIF('Functional Scenarios'!C2:C93,"caregiver")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -957,7 +956,7 @@
         <x:v>Configuration</x:v>
       </x:c>
       <x:c r="E11" t="n">
-        <x:f>COUNTIF('Functional Scenarios'!C2:C69,"configuration")</x:f>
+        <x:f>COUNTIF('Functional Scenarios'!C2:C93,"configuration")</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -966,13 +965,13 @@
         <x:v>Browser automation</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>MANUAL_REQUIRED</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="D12" t="str">
         <x:v>Negative</x:v>
       </x:c>
       <x:c r="E12" t="n">
-        <x:f>COUNTIF('Functional Scenarios'!C2:C69,"negative")</x:f>
+        <x:f>COUNTIF('Functional Scenarios'!C2:C93,"negative")</x:f>
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -987,7 +986,7 @@
         <x:v>Diagnostics</x:v>
       </x:c>
       <x:c r="E13" t="n">
-        <x:f>COUNTIF('Functional Scenarios'!C2:C69,"diagnostics")</x:f>
+        <x:f>COUNTIF('Functional Scenarios'!C2:C93,"diagnostics")</x:f>
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -1019,10 +1018,10 @@
         <x:v>BROWSER/PWA</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>MANUAL_REQUIRED</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="C17" s="12" t="str">
-        <x:v>Playwright not installed in current evidence environment; use generated manual plan or make release-gate-browser.</x:v>
+        <x:v>Playwright desktop/mobile validation passed; make release-gate-final is mandatory for browser-qualified releases.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1077,10 +1076,10 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="12" t="str">
-        <x:v>make release-gate-browser</x:v>
+        <x:v>make release-gate-final</x:v>
       </x:c>
       <x:c r="B24" s="12" t="str">
-        <x:v>Full gate with browser automation mandatory</x:v>
+        <x:v>Mandatory preflight plus desktop/mobile PWA browser gate</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -14406,7 +14405,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C13" s="12" t="str">
-        <x:v>80 C++ checks</x:v>
+        <x:v>94 C++ checks</x:v>
       </x:c>
       <x:c r="D13" s="12" t="str">
         <x:v>Yes</x:v>
@@ -14443,16 +14442,16 @@
         <x:v>Playwright browser</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
-        <x:v>MANUAL_REQUIRED</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="C15" s="12" t="str">
-        <x:v>Playwright not installed; generated manual plan provided</x:v>
+        <x:v>Mandatory desktop/mobile Chromium validation passed via make release-gate-final</x:v>
       </x:c>
       <x:c r="D15" s="12" t="str">
         <x:v>Browser-specific</x:v>
       </x:c>
       <x:c r="E15" s="12" t="str">
-        <x:v>node tests/simulation_browser_test.cjs / make release-gate-browser</x:v>
+        <x:v>node tests/simulation_browser_test.cjs / make release-gate-final</x:v>
       </x:c>
       <x:c r="F15" s="40" t="str">
         <x:v>v1.5.4</x:v>
